--- a/docs/150526_enhancement_status_for_consultants.xlsx
+++ b/docs/150526_enhancement_status_for_consultants.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Items" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Discussion points" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Round 2 status (current)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +72,12 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +109,12 @@
         <fgColor rgb="00FECACA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00336B24"/>
+        <bgColor rgb="00336B24"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -155,6 +166,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1464,4 +1481,735 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>What was done</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Scenario 6: Optimization fails when Risk factor = 0</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Removed the stale service-layer guard in manpower_app/service.py that raised ValueError when risk_factor &lt;= 0. The LP itself is R=0-safe; the constraint O*(1-R)+I&gt;=M degenerates to O+I&gt;=M (sound). End-to-end pytest scenario added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Scenario 5: Management Saudization rate ignored for 'Management' job family</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>'Management' is a distinct job family from 'Executive Management' in mappings.py. Added it to the profession_saudization_rates dict in service.py (both call sites). Per-profession Management rate now applies to BOTH families.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Scenario 1: Tool prefers in-house when workbook outsourced cost is higher (safety officers)</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Added cap_outsourced_at_inhouse() in costs.py. When the workbook's outsourced cost is higher than in-house non-Saudi (data inversion), it is capped at in-house so the LP can no longer ignore the outsourceability rule on cost grounds. Mirrors the Saudi premium clamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Scenario 8: Insurance + service margin not applied to all job families</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Two-part fix: (a) removed the legacy min(service_margin, 500) clamp in costs.py that silently truncated workbook values; (b) the negotiated-cost formula now falls back to Avg Cost Outsourced when 'Excluding Insurance Service' is NA, so insurance+margin reach families that have no subcontractor rows in the payroll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Scenario 8 follow-up: cost-inversion cap must not break user-driven negotiated rates</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Moved the cost-inversion cap to apply BEFORE negotiated insurance+margin are added. The user can still legitimately push outsourced above in-house via the scenario knob; the cap only fixes raw workbook data inversion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Saudization toggle on/off should disable the rate slider when off</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Slider is greyed out when 'Enforce overall Saudization' is off (parallel to the existing tenure-protection pattern).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Dynamic Saudi protection percentage (not 0/100% only)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Replaced the binary can_reduce_current_saudi with protect_current_saudi_percent (0.0-1.0). The LP's _saudi_lower_bound uses round(current_saudi * pct) when supplied. Legacy boolean preserved for back-compat. UI surfaces it as a percentage input with sensible defaults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Output bars: legend with IS / IN / O short codes</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Bar segments use the short codes (In-house Saudi / In-house Non-Saudi / Outsourced) so the label fits even on the narrowest slices. A legend row above each family bar group explains the codes once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Pre/post Saudization rate under the donut charts</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>In Optimize Current Manpower mode, each donut now shows the Saudization % beneath: Current Saudization X% on the left, Optimized Saudization Y% on the right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Move Optimization Mode selection to right after Data Upload (was inside User Assumptions)</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>New 'Optimization Mode' stage inserted between Data Upload and Additional Inputs. Two large radio cards (Optimize Current vs Target Manpower Plan). Removed the duplicate mode block from User Assumptions. Fixes Saad's 'jump back one step' UX note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>BU Selection workflow stage (#4 + #17)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>New 'BU Selection' step between Home and Data Upload. Tile grid with the 9 CPC subsidiaries (MGIC seeded as preconfigured by default; others empty until the user uploads their config). Click any tile to open its Configuration view; the 'Use this BU' button activates it and advances to Data Upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Map a new profession to an EXISTING job family on the Mappings step</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>When the uploaded payroll has an unmapped pair (e.g. 'Quarries - Senior Labor'), the user can now route it to an existing canonical family ('Skilled Labor') with a dropdown alongside the existing 'Define new job family' wizard. Persisted as payroll_pair_overrides; replayed on re-upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>BU Configuration via Excel (read-only UI viewer)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Per-BU Configuration panel shows the BU's outsourceability, ratios, and drivers in read-only tables. Excel is the SINGLE source of truth for editing; the user downloads the workbook, edits, and re-uploads. Single 'Value' column per row (no Default/Override duality). Sticky section navigator at the top with jump-anchors so 39 outsourceability rows do not hide the other sections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>BU Configuration applies to optimization end-to-end</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Backend: rules.py exposes get_outsourceability_rules(overrides) and get_maximum_ratio_rules(overrides); ratios.py:calculate_driver_values accepts driver_overrides. prepare_model_data re-derives Outsourceability Type, Maximum Ratio, Driver Value, and Minimum Headcount Needed per family when overrides are supplied. Streamlit unaffected via defaults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>MGIC ships preconfigured; other BUs start empty</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>BUConfigurationPanel auto-seeds MGIC's configuration on first open from /assumptions/defaults. Other BUs (UAAC, FAST, SACODECO, Sphinx, Premco Precast, Premco Ready Mix, Bahra Steel, UCC) show the empty state with a 'Download starter Excel' CTA until the user uploads BU-specific values. The starter Excel lists every canonical family in column A with a blank Value column to fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Excel template validation (no silent partial saves)</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>parse_workbook validates each row: outsourceability values must be one of the 3 canonical strings, ratios must match the '1:N' pattern, ratios with whitespace are normalized. Invalid rows are reported with row-level error messages and never silently applied. Tested for mixed valid/invalid input, missing sheets, and legacy back-compat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Saudi pay premium / outsource discount belong in User Assumptions (scenario), not BU Excel</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Removed the 'Engine Knobs' sheet from the BU workbook entirely. Saudi pay premium and Outsource cost discount are now scenario knobs on User Assumptions only. The BU workbook now has 4 sheets: README, Outsourceability, Ratios, Drivers (true per-BU constraints only). Legacy workbooks with the old Engine Knobs sheet still parse correctly (back-compat preserved).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Renamed 'Saudi cost premium' to 'Saudi pay premium' for client clarity</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Clearer label for the multiplier applied to non-Saudi in-house cost (e.g. 1.10x means Saudis cost 10% more). Internal field name unchanged to avoid breaking persistence/legacy payloads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>BU Selection page polished and compact (all 9 BUs on one screen)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Hero header with CPC Holding mark + title. 3x3 card grid (responsive: 2-col tablet, 1-col phone). Each card shows: status pill (Custom configured / Using tool defaults), logo plate, BU code + full name, CTA + animated arrow. Stagger fade-up entry animation; hover lift + logo scale + accent border. No scroll: hero ~80px + 3 rows of ~180px cards fits comfortably.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>BU logos sourced from cpcholding.com</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Done with caveat</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Downloaded real high-quality logos from cpcholding.com for MGIC, UAAC, SACODECO, FAST, Premco Precast, Premco Ready Mix, Bahra Steel. Sphinx, UCC, and a dark-on-light CPC Holding mark were not found at acceptable quality online. Currently all logos are temporarily disabled per consultant request; every BU tile renders a clean typographic placeholder (BU code in display-serif) until proper brand assets are dropped into desktop/src/assets/bu-logos/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Configuration panel: 'Edit configuration via Excel' redesigned</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Two-step card layout (Step 1: Download, Step 2: Upload) with icons, numbered step pills, hover/lift animations. The upload card is a drag-and-drop zone (drop your .xlsx anywhere in the card) with active-drag visual feedback. Validation errors shown inline; status banner above/below indicates success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Removed all em-dashes from user-facing copy</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Replaced em-dashes with periods, commas, or colons across BUSelectionWorkspace, MappingResolveWorkspace, ScenarioControls, ResultsDashboard, AppShell, and supporting copy. Cleaner reading flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Removed duplicate 'Continue' / 'Next' buttons</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>The AppShell renders a Previous/Next stage navigator at the bottom of every step. Removed redundant inline 'Continue to User Assumptions' on the Mappings step and 'Continue to Additional Inputs' on the Mode step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>9 Debugging-sheet scenarios codified as pytest regressions</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>tests/test_optimization.py has DebuggingScenarioTests covering Scenarios 1, 5, 6, 8 + helper tests for the fixed behaviors. Future code changes can no longer silently re-introduce any of these consultant-reported bugs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>End-to-end user journey + edge-case coverage</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Test suite expanded to 56 tests across 14 classes (3 skip on this machine because they require the consultant's local workbook fixture). Covers: BU overrides reaching the LP, BU isolation, target mode + BU overrides combined, target mode + scenario cost knobs combined, Excel round-trip with mixed valid/invalid rows, HTTP wire-layer smoke tests for /health, /assumptions/defaults, /bu/configuration/*, and the full upload-then-optimize cycle over JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Hi-res CPC logo (high-quality dark version on transparent background)</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Only the white-on-transparent variant is available on cpcholding.com (not usable on light backgrounds). Need Saad to share a proper transparent-background dark mark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>'How the tool works' / Help tab</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Per the consultant's workbook note, this needs Tarek (principal) alignment before we build it. Not in scope this round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Sphinx, UCC individual logos + dark CPC Holding mark</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Not on the current cpcholding.com portfolio (UCC, Sphinx) or only available as white-on-transparent (CPC). Drop high-quality PNGs into desktop/src/assets/bu-logos/ and add the logoSrc field in BUSelectionWorkspace.tsx to wire them in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Saudization rates as BU constraints (vs scenario knobs)</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Saad's original spec grouped Saudization under User Assumptions, but it could arguably live in BU configuration as a regulatory constraint per industry. Not changed in this round; kept as scenario inputs. Easy to move later if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Frontend UI click-automation (Playwright/Cypress)</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Out of scope</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Optimizer logic, HTTP wire layer, and Python data flow are all auto-tested. UI rendering and button wiring are verified via in-browser smoke testing. Adding automated UI tests is recommended before client handoff but is a separate effort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Streamlit changes</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Out of scope</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Same scope as PR #1. The rules.py refactor preserves module-level constants for back-compat so Streamlit continues to work unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Generated 2026-05-18 - 150526 batch 2 enhancements (consolidated update).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>